--- a/Data_Analysis/Sensitivity analysis/Hybrid/sweep_results_hybrid_G2_task067.xlsx
+++ b/Data_Analysis/Sensitivity analysis/Hybrid/sweep_results_hybrid_G2_task067.xlsx
@@ -100,7 +100,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N3"/>
+  <dimension ref="A1:N5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="7.85546875" customWidth="true"/>
@@ -251,6 +251,94 @@
         <v>5.4865137124002388</v>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="0">
+        <v>414</v>
+      </c>
+      <c r="B4" s="0">
+        <v>267</v>
+      </c>
+      <c r="C4" s="0">
+        <v>414</v>
+      </c>
+      <c r="D4" s="0">
+        <v>80.5993281368212</v>
+      </c>
+      <c r="E4" s="0">
+        <v>462.26999999999998</v>
+      </c>
+      <c r="F4" s="0">
+        <v>159.3259181290953</v>
+      </c>
+      <c r="G4" s="0">
+        <v>55296.655127992701</v>
+      </c>
+      <c r="H4" s="0">
+        <v>-8941.5335775962394</v>
+      </c>
+      <c r="I4" s="0">
+        <v>5.7300000000000004</v>
+      </c>
+      <c r="J4" s="0">
+        <v>14.620000000000001</v>
+      </c>
+      <c r="K4" s="0">
+        <v>2.2850000000000001</v>
+      </c>
+      <c r="L4" s="0">
+        <v>3.3050000000000002</v>
+      </c>
+      <c r="M4" s="0">
+        <v>300.03062254639877</v>
+      </c>
+      <c r="N4" s="0">
+        <v>5.4865137124002388</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="0">
+        <v>414</v>
+      </c>
+      <c r="B5" s="0">
+        <v>268</v>
+      </c>
+      <c r="C5" s="0">
+        <v>414</v>
+      </c>
+      <c r="D5" s="0">
+        <v>80.599328139590781</v>
+      </c>
+      <c r="E5" s="0">
+        <v>462.26999999999998</v>
+      </c>
+      <c r="F5" s="0">
+        <v>159.3259181290953</v>
+      </c>
+      <c r="G5" s="0">
+        <v>55296.655127408332</v>
+      </c>
+      <c r="H5" s="0">
+        <v>-8941.5335778476801</v>
+      </c>
+      <c r="I5" s="0">
+        <v>5.7300000000000004</v>
+      </c>
+      <c r="J5" s="0">
+        <v>14.620000000000001</v>
+      </c>
+      <c r="K5" s="0">
+        <v>2.2850000000000001</v>
+      </c>
+      <c r="L5" s="0">
+        <v>3.3050000000000002</v>
+      </c>
+      <c r="M5" s="0">
+        <v>300.0306225463948</v>
+      </c>
+      <c r="N5" s="0">
+        <v>5.4865137124002388</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>